--- a/erp-server/erp-server-wms/src/main/resources/excel/poReturnExport.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/poReturnExport.xlsx
@@ -174,7 +174,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -183,6 +183,15 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="10"/>
       <color theme="1"/>
       <name val="宋体"/>
@@ -190,9 +199,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -339,12 +356,24 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.05"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.15"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -674,58 +703,52 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -737,84 +760,96 @@
     <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1193,143 +1228,143 @@
     <col min="24" max="24" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23">
-      <c r="A1" s="1" t="s">
+    <row r="1" s="1" customFormat="1" spans="1:23">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="T1" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" s="2" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:23">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="J2" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3" t="s">
+      <c r="K2" s="4"/>
+      <c r="L2" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="M2" s="3" t="s">
+      <c r="M2" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="N2" s="3" t="s">
+      <c r="N2" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="O2" s="3" t="s">
+      <c r="O2" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="P2" s="3" t="s">
+      <c r="P2" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="Q2" s="3" t="s">
+      <c r="Q2" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="R2" s="3" t="s">
+      <c r="R2" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="S2" s="3" t="s">
+      <c r="S2" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="T2" s="3" t="s">
+      <c r="T2" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="U2" s="3" t="s">
+      <c r="U2" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="V2" s="3" t="s">
+      <c r="V2" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="W2" s="3" t="s">
+      <c r="W2" s="4" t="s">
         <v>44</v>
       </c>
     </row>

--- a/erp-server/erp-server-wms/src/main/resources/excel/poReturnExport.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/poReturnExport.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
   <si>
     <t>退货单号</t>
   </si>
@@ -125,7 +125,10 @@
     <t>{.billDate}</t>
   </si>
   <si>
-    <t>{.confirmDate}{.returnWarehouseName}</t>
+    <t>{.confirmDate}</t>
+  </si>
+  <si>
+    <t>{.returnWarehouseName}</t>
   </si>
   <si>
     <t>{.returnQty}</t>
@@ -1212,8 +1215,8 @@
     <col min="7" max="7" width="12.75" customWidth="1"/>
     <col min="8" max="8" width="28.75" customWidth="1"/>
     <col min="9" max="9" width="13" customWidth="1"/>
-    <col min="10" max="10" width="10.75" customWidth="1"/>
-    <col min="11" max="11" width="20.375" customWidth="1"/>
+    <col min="10" max="10" width="16.125" customWidth="1"/>
+    <col min="11" max="11" width="23.375" customWidth="1"/>
     <col min="12" max="12" width="9.25" customWidth="1"/>
     <col min="13" max="13" width="22.125" customWidth="1"/>
     <col min="14" max="14" width="12.125" customWidth="1"/>
@@ -1330,42 +1333,44 @@
       <c r="J2" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="K2" s="4"/>
+      <c r="K2" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="L2" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P2" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="R2" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="S2" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="U2" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="V2" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="W2" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-wms/src/main/resources/excel/poReturnExport.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/poReturnExport.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="24045" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
   <si>
     <t>退货单号</t>
   </si>
@@ -53,6 +53,9 @@
     <t>产品名称</t>
   </si>
   <si>
+    <t>是否组合品</t>
+  </si>
+  <si>
     <t>退货日期</t>
   </si>
   <si>
@@ -120,6 +123,9 @@
   </si>
   <si>
     <t>{.productName}</t>
+  </si>
+  <si>
+    <t>{.isCombinationName}</t>
   </si>
   <si>
     <t>{.billDate}</t>
@@ -1203,7 +1209,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W2"/>
+  <dimension ref="A1:X2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="15.625" customWidth="1"/>
@@ -1214,24 +1220,24 @@
     <col min="6" max="6" width="7.375" customWidth="1"/>
     <col min="7" max="7" width="12.75" customWidth="1"/>
     <col min="8" max="8" width="28.75" customWidth="1"/>
-    <col min="9" max="9" width="13" customWidth="1"/>
-    <col min="10" max="10" width="16.125" customWidth="1"/>
-    <col min="11" max="11" width="23.375" customWidth="1"/>
-    <col min="12" max="12" width="9.25" customWidth="1"/>
-    <col min="13" max="13" width="22.125" customWidth="1"/>
-    <col min="14" max="14" width="12.125" customWidth="1"/>
-    <col min="15" max="15" width="8" customWidth="1"/>
-    <col min="16" max="16" width="7.875" customWidth="1"/>
-    <col min="17" max="17" width="19.75" customWidth="1"/>
-    <col min="18" max="18" width="10.625" customWidth="1"/>
-    <col min="19" max="19" width="23.625" customWidth="1"/>
-    <col min="21" max="21" width="9.625" customWidth="1"/>
-    <col min="22" max="22" width="8.25" customWidth="1"/>
-    <col min="23" max="23" width="22.125" customWidth="1"/>
-    <col min="24" max="24" width="18" customWidth="1"/>
+    <col min="9" max="10" width="13" customWidth="1"/>
+    <col min="11" max="11" width="16.125" customWidth="1"/>
+    <col min="12" max="12" width="23.375" customWidth="1"/>
+    <col min="13" max="13" width="9.25" customWidth="1"/>
+    <col min="14" max="14" width="22.125" customWidth="1"/>
+    <col min="15" max="15" width="12.125" customWidth="1"/>
+    <col min="16" max="16" width="8" customWidth="1"/>
+    <col min="17" max="17" width="7.875" customWidth="1"/>
+    <col min="18" max="18" width="19.75" customWidth="1"/>
+    <col min="19" max="19" width="10.625" customWidth="1"/>
+    <col min="20" max="20" width="23.625" customWidth="1"/>
+    <col min="22" max="22" width="9.625" customWidth="1"/>
+    <col min="23" max="23" width="8.25" customWidth="1"/>
+    <col min="24" max="24" width="22.125" customWidth="1"/>
+    <col min="25" max="25" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:23">
+    <row r="1" s="1" customFormat="1" spans="1:24">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1268,7 +1274,7 @@
       <c r="L1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="5" t="s">
         <v>12</v>
       </c>
       <c r="N1" s="2" t="s">
@@ -1289,10 +1295,10 @@
       <c r="S1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="T1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="U1" s="3" t="s">
         <v>20</v>
       </c>
       <c r="V1" s="2" t="s">
@@ -1301,76 +1307,82 @@
       <c r="W1" s="2" t="s">
         <v>22</v>
       </c>
+      <c r="X1" s="2" t="s">
+        <v>23</v>
+      </c>
     </row>
-    <row r="2" spans="1:23">
+    <row r="2" spans="1:24">
       <c r="A2" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P2" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="R2" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="S2" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="U2" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="V2" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="W2" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="X2" s="4" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
